--- a/data/trans_orig/P1407-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2012</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11803</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>302474</t>
+          <t>302780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312447</t>
+          <t>312399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739862</t>
+          <t>740278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749654</t>
+          <t>749659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412870</t>
+          <t>413841</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325724</t>
+          <t>326465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336206</t>
+          <t>336225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741544</t>
+          <t>743561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754906</t>
+          <t>754912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620066</t>
+          <t>619171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628411</t>
+          <t>628351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248081</t>
+          <t>247996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258168</t>
+          <t>258019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>870847</t>
+          <t>871078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>884492</t>
+          <t>884482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>23104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24930</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1151599</t>
+          <t>1152481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742741</t>
+          <t>741618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>757456</t>
+          <t>757470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1898801</t>
+          <t>1898379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914589</t>
+          <t>1914667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35569</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500181</t>
+          <t>501999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509587</t>
+          <t>509588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>728897</t>
+          <t>727782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747332</t>
+          <t>747353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1235274</t>
+          <t>1235436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1255713</t>
+          <t>1256067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32522</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>34134</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1075647</t>
+          <t>1074643</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1094689</t>
+          <t>1094349</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1340977</t>
+          <t>1340917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1361475</t>
+          <t>1361316</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54735</t>
+          <t>56427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89360</t>
+          <t>91652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64358</t>
+          <t>65016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100362</t>
+          <t>98891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3403262</t>
+          <t>3403150</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3416888</t>
+          <t>3416729</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3456372</t>
+          <t>3454080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3490997</t>
+          <t>3489305</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6867280</t>
+          <t>6868751</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6903284</t>
+          <t>6902626</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2016</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419310</t>
+          <t>418503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428056</t>
+          <t>428051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333785</t>
+          <t>333479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344939</t>
+          <t>345068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757270</t>
+          <t>756265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771131</t>
+          <t>771329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3709,97 +3709,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5231</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1039</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6511</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377227</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367069</t>
+          <t>367042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742989</t>
+          <t>744249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515571</t>
+          <t>515647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155109</t>
+          <t>155333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164962</t>
+          <t>164969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>674547</t>
+          <t>674109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685690</t>
+          <t>685939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28164</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1135319</t>
+          <t>1134828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146715</t>
+          <t>1146831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>807703</t>
+          <t>807315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820925</t>
+          <t>821012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1947350</t>
+          <t>1947628</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965159</t>
+          <t>1964852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>613901</t>
+          <t>614128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619939</t>
+          <t>619941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712990</t>
+          <t>712500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>729290</t>
+          <t>729498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1329374</t>
+          <t>1330691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1348345</t>
+          <t>1348002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>33996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281972</t>
+          <t>282512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1047355</t>
+          <t>1048029</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1068696</t>
+          <t>1068177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1332811</t>
+          <t>1331203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1354666</t>
+          <t>1354417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44446</t>
+          <t>43285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75622</t>
+          <t>77554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58738</t>
+          <t>58990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93860</t>
+          <t>95702</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3359659</t>
+          <t>3359765</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3375409</t>
+          <t>3375957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3455974</t>
+          <t>3454042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3487150</t>
+          <t>3488311</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6823458</t>
+          <t>6821616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6858580</t>
+          <t>6858328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P1407-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Clase-trans_orig.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>12446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>302780</t>
+          <t>303062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312399</t>
+          <t>312430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740278</t>
+          <t>739219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749659</t>
+          <t>749626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413841</t>
+          <t>413797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326465</t>
+          <t>326342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336225</t>
+          <t>336217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>743561</t>
+          <t>742487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754912</t>
+          <t>754863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619171</t>
+          <t>618867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628351</t>
+          <t>628378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247996</t>
+          <t>248096</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258019</t>
+          <t>258041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871078</t>
+          <t>871909</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>884482</t>
+          <t>884492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1152481</t>
+          <t>1152023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741618</t>
+          <t>742803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>757470</t>
+          <t>757588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1898379</t>
+          <t>1899281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914667</t>
+          <t>1914662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32464</t>
+          <t>30741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35407</t>
+          <t>34439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>501999</t>
+          <t>502086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509588</t>
+          <t>509585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727782</t>
+          <t>729505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747353</t>
+          <t>747965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1235436</t>
+          <t>1236404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1256067</t>
+          <t>1256896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33526</t>
+          <t>33633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34134</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1074643</t>
+          <t>1074536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1094349</t>
+          <t>1094430</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1340917</t>
+          <t>1340693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1361316</t>
+          <t>1360648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>55041</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91652</t>
+          <t>90703</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65016</t>
+          <t>64599</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3403150</t>
+          <t>3403285</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3416729</t>
+          <t>3416888</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3454080</t>
+          <t>3455029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3489305</t>
+          <t>3490691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6868751</t>
+          <t>6866965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6902626</t>
+          <t>6903043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19882</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418503</t>
+          <t>418254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428051</t>
+          <t>428061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333479</t>
+          <t>334100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345068</t>
+          <t>345062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756265</t>
+          <t>757587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771329</t>
+          <t>771217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367042</t>
+          <t>366803</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>744249</t>
+          <t>743262</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515647</t>
+          <t>515557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155333</t>
+          <t>155690</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164969</t>
+          <t>164931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>674109</t>
+          <t>675149</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685939</t>
+          <t>685513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18561</t>
+          <t>18964</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1134828</t>
+          <t>1134375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146831</t>
+          <t>1146349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>807315</t>
+          <t>806912</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821012</t>
+          <t>820620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1947628</t>
+          <t>1949038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964852</t>
+          <t>1965487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25744</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>614128</t>
+          <t>613461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712500</t>
+          <t>711804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>729498</t>
+          <t>728761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1330691</t>
+          <t>1330308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1348002</t>
+          <t>1348638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>34205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37967</t>
+          <t>35611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282512</t>
+          <t>282756</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1048029</t>
+          <t>1047820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1068177</t>
+          <t>1069496</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1331203</t>
+          <t>1333559</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1354417</t>
+          <t>1354399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25957</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43285</t>
+          <t>45473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>77265</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58990</t>
+          <t>59070</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95702</t>
+          <t>96518</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3359765</t>
+          <t>3359566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3375957</t>
+          <t>3375850</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3454042</t>
+          <t>3454331</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3488311</t>
+          <t>3486123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6821616</t>
+          <t>6820800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6858328</t>
+          <t>6858248</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
